--- a/- Hash Convencional.xlsx
+++ b/- Hash Convencional.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3E44EF-FA8D-4BA0-9E87-D3F388D9FCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7E4103-8837-4744-88AE-589452CCB64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="20" r:id="rId1"/>
     <sheet name="WashingtonDatabase" sheetId="21" r:id="rId2"/>
+    <sheet name="MountainDatabase" sheetId="22" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="119">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -373,6 +374,27 @@
   </si>
   <si>
     <t>43b4f1d06dcb6c584a8fe87cc9104a7c4092ab04bf649ec1b04f884cb1f6252f</t>
+  </si>
+  <si>
+    <t>ee07bb8f2c127818b7937d916625cdec</t>
+  </si>
+  <si>
+    <t>Alternative (1)</t>
+  </si>
+  <si>
+    <t>f014c80d1180d0c475dae658caeb50d8</t>
+  </si>
+  <si>
+    <t>b568dc0fa979fb62c40abdc34461374590ba8647</t>
+  </si>
+  <si>
+    <t>d0dfdd0032a13286f0b5f2e80f65998a57f905ec</t>
+  </si>
+  <si>
+    <t>2f5ef85537cff9955de11644329785588d41699f302f6c0cbd2cdf716d892118</t>
+  </si>
+  <si>
+    <t>f2eeba88662c53f696ad058c483694822925babdf2a883dd0020de463c6ae308</t>
   </si>
 </sst>
 </file>
@@ -1208,4 +1230,170 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0BFC08-6082-4292-916D-F5AFAF8E32EA}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="68.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/- Hash Convencional.xlsx
+++ b/- Hash Convencional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7E4103-8837-4744-88AE-589452CCB64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A53564-F279-4734-B645-F55747AD8DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="157">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -395,6 +395,120 @@
   </si>
   <si>
     <t>f2eeba88662c53f696ad058c483694822925babdf2a883dd0020de463c6ae308</t>
+  </si>
+  <si>
+    <t>Alternative (2)</t>
+  </si>
+  <si>
+    <t>Alternative (3)</t>
+  </si>
+  <si>
+    <t>Alternative (4)</t>
+  </si>
+  <si>
+    <t>Alternative (5)</t>
+  </si>
+  <si>
+    <t>Alternative (6)</t>
+  </si>
+  <si>
+    <t>Alternative (7)</t>
+  </si>
+  <si>
+    <t>Alternative (8)</t>
+  </si>
+  <si>
+    <t>Alternative (9)</t>
+  </si>
+  <si>
+    <t>Alternative (10)</t>
+  </si>
+  <si>
+    <t>Alternative (11)</t>
+  </si>
+  <si>
+    <t>Alternative (12)</t>
+  </si>
+  <si>
+    <t>Alternative (13)</t>
+  </si>
+  <si>
+    <t>Alternative (14)</t>
+  </si>
+  <si>
+    <t>Alternative (15)</t>
+  </si>
+  <si>
+    <t>Alternative (16)</t>
+  </si>
+  <si>
+    <t>Alternative (17)</t>
+  </si>
+  <si>
+    <t>Alternative (18)</t>
+  </si>
+  <si>
+    <t>Alternative (19)</t>
+  </si>
+  <si>
+    <t>Alternative (20)</t>
+  </si>
+  <si>
+    <t>Alternative (21)</t>
+  </si>
+  <si>
+    <t>Alternative (22)</t>
+  </si>
+  <si>
+    <t>Alternative (23)</t>
+  </si>
+  <si>
+    <t>Alternative (24)</t>
+  </si>
+  <si>
+    <t>Alternative (25)</t>
+  </si>
+  <si>
+    <t>Alternative (26)</t>
+  </si>
+  <si>
+    <t>Alternative (27)</t>
+  </si>
+  <si>
+    <t>Alternative (28)</t>
+  </si>
+  <si>
+    <t>Alternative (29)</t>
+  </si>
+  <si>
+    <t>Alternative (30)</t>
+  </si>
+  <si>
+    <t>2694faf0dcf3ab267e58d7ace2f8c7fd</t>
+  </si>
+  <si>
+    <t>f3ff9705475e8bad93a11e9ebbf08b022d80dcba</t>
+  </si>
+  <si>
+    <t>184806d890e2b6c93439981cc7dd53c81ca809a94f1fc9c1ca77efec47f52956</t>
+  </si>
+  <si>
+    <t>88725b2c1449ced46a7e7d6833148ea1</t>
+  </si>
+  <si>
+    <t>c190ac8578afc63a972eb00d37c3badc945e4b97</t>
+  </si>
+  <si>
+    <t>9c40e4de6a3a4742c1b20776f724b082709bbc67d19fb0b697fabeb008bce73b</t>
+  </si>
+  <si>
+    <t>a85ddefa98380886f22fa12c8f4024e1</t>
+  </si>
+  <si>
+    <t>570b3beabaaaa47a462047e5b0511a02be101571</t>
+  </si>
+  <si>
+    <t>5de9e9ffcf2ecd78510f1f5665698531397d7c754d60f9d7c8c9870487343e13</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0BFC08-6082-4292-916D-F5AFAF8E32EA}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
@@ -1286,112 +1400,254 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="A4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="A5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="A6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>122</v>
+      </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
+      <c r="A12" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
+      <c r="A15" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
+      <c r="A16" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
+      <c r="A17" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
+      <c r="A18" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
+      <c r="A19" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
+      <c r="A20" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="B20" s="1"/>
       <c r="C20" s="7"/>
       <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
+      <c r="A21" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/- Hash Convencional.xlsx
+++ b/- Hash Convencional.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A53564-F279-4734-B645-F55747AD8DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F28917-F504-429E-BF98-DB769B8B2819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="20" r:id="rId1"/>
-    <sheet name="WashingtonDatabase" sheetId="21" r:id="rId2"/>
-    <sheet name="MountainDatabase" sheetId="22" r:id="rId3"/>
+    <sheet name="MountainDatabase" sheetId="22" r:id="rId2"/>
+    <sheet name="WashingtonDatabase" sheetId="21" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="196">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -509,6 +509,123 @@
   </si>
   <si>
     <t>5de9e9ffcf2ecd78510f1f5665698531397d7c754d60f9d7c8c9870487343e13</t>
+  </si>
+  <si>
+    <t>88e3bdba58658aab13ff927ec9c5fdef</t>
+  </si>
+  <si>
+    <t>9c91066cc83c91892692d1dbabcd5773c620b159</t>
+  </si>
+  <si>
+    <t>7f851fc8e7960c539d6799ec040c0ed5c42d2aef5235e9d1560bfff151007ffe</t>
+  </si>
+  <si>
+    <t>2b897b6c1bf79bf10cfeca8fe7839128</t>
+  </si>
+  <si>
+    <t>ea0909d275e5bc0dd7807dbdfe45e46e1b204553</t>
+  </si>
+  <si>
+    <t>6394dfd2558b55e5b4bb009b27c1edaafb44bafa09b293cad09eabf49f8c74cb</t>
+  </si>
+  <si>
+    <t>f337041e7d839fd4e3d90b2e9a2ef613</t>
+  </si>
+  <si>
+    <t>55669c73cbb42f638f18cb2ca24aa89f34cf674d</t>
+  </si>
+  <si>
+    <t>dc768c9f550178052e9c2c4d717ccdc0fb41629e852949e28517bb73b541296e</t>
+  </si>
+  <si>
+    <t>85fda76dc702f92950dadedb982665d8</t>
+  </si>
+  <si>
+    <t>f6ca5fb0faeec98bf5d701c7c9ec4c93a63945ad</t>
+  </si>
+  <si>
+    <t>0631eaaedb79a873e4e3089357e9084cef444bbc29b2286c90d7d8216470ece8</t>
+  </si>
+  <si>
+    <t>0e1fca0ac4c36a9264357ce3bb22b3ab</t>
+  </si>
+  <si>
+    <t>2263b0b29242996faa782f02ba2da6c3db7a4120</t>
+  </si>
+  <si>
+    <t>db332563cf29b496804d908e929b250d9cd2a3afa284f8f50f2d546396482696</t>
+  </si>
+  <si>
+    <t>9862129024de8419d47c322491706d22</t>
+  </si>
+  <si>
+    <t>6aa0df24a74ed26e80b4f2defe4671d212a26a95</t>
+  </si>
+  <si>
+    <t>e354aa4c6dfc6eefbea29d865f47bd394eac6bd53fb88a4adf79cfb69bd4bb40</t>
+  </si>
+  <si>
+    <t>6ca8e84b88b63dc17443fff919f9fa3c</t>
+  </si>
+  <si>
+    <t>1137a449dfef6edf48484910e161c3a951791ff4</t>
+  </si>
+  <si>
+    <t>baea1673c9f3c553b4ef84fd3037b4aebe02c31389387cb19b4310e8d41a3f65</t>
+  </si>
+  <si>
+    <t>6e1daea721277210ff662d2747f9733d</t>
+  </si>
+  <si>
+    <t>88a1b5175f979aec110d631985a70d628eefb722</t>
+  </si>
+  <si>
+    <t>5da641dfbc58aaa1bbd6271ed99d1ea8cc9e87b74604d7c9784ad6ad672f24e7</t>
+  </si>
+  <si>
+    <t>f07b823dbe4af1b0c5589786b8a17544</t>
+  </si>
+  <si>
+    <t>420e3a1df07e4a1ebd880636b2d1fe748416c683</t>
+  </si>
+  <si>
+    <t>e33e293d0bf26eb3c99e7fd42e3d59b79364d15f2ee2de1fec5bf1bd1d16368d</t>
+  </si>
+  <si>
+    <t>e41fb32c57a834c78da2f8b632eff011</t>
+  </si>
+  <si>
+    <t>a526a97f407b8ceb63beab93028a70f47c80f840</t>
+  </si>
+  <si>
+    <t>07b791db6257fdb0608cd26e45915da2cc963330bccedddc5f85257151f1c79f</t>
+  </si>
+  <si>
+    <t>4a00890ded54253e83a7f855ce5c56c55adceda05b12715579d98065d08e35ae</t>
+  </si>
+  <si>
+    <t>1f6cb8a902be00ba10e89cf770a87f8eb4933a0f</t>
+  </si>
+  <si>
+    <t>7a847749e9f68ced45671acd9935f964</t>
+  </si>
+  <si>
+    <t>1ef1ef6ac9814b297304478c4ee7a250bbc895380fcad5e07441cf34428c7de4</t>
+  </si>
+  <si>
+    <t>a4452dc9e8c97b36ec166944ca494f4a3dc4a30d</t>
+  </si>
+  <si>
+    <t>e5ad9838f9e58f5d48726bc9ca7a9f44</t>
+  </si>
+  <si>
+    <t>9050f20ff5e906c053bbb7161d52fe9c</t>
+  </si>
+  <si>
+    <t>4c05a48c0d2f0c464d6776323c3af2c80fbd75c6</t>
+  </si>
+  <si>
+    <t>6e72ce1e1d97f94667853bbdd5a79205206b3bfa0a11730ee3c560b28c2546cc</t>
   </si>
 </sst>
 </file>
@@ -585,7 +702,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -596,6 +713,7 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1219,6 +1337,396 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0BFC08-6082-4292-916D-F5AFAF8E32EA}">
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D37" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4653D079-C8C7-4EFD-B691-42F479BD5FAB}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1344,312 +1852,4 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0BFC08-6082-4292-916D-F5AFAF8E32EA}">
-  <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="68.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="7"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
 </file>
--- a/- Hash Convencional.xlsx
+++ b/- Hash Convencional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F28917-F504-429E-BF98-DB769B8B2819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053AA5A2-03AE-440D-A5F7-48914F8667EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="199">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -626,13 +626,22 @@
   </si>
   <si>
     <t>6e72ce1e1d97f94667853bbdd5a79205206b3bfa0a11730ee3c560b28c2546cc</t>
+  </si>
+  <si>
+    <t>907f05f2ca68b71736fa841138dbab07</t>
+  </si>
+  <si>
+    <t>c9d254f53b6ace068665f1d1028b3ed67b66e88d</t>
+  </si>
+  <si>
+    <t>662b29a7ae7fe0c2e051628d020905d0faa54f05cfa1c4036801fe02219db3d7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -647,6 +656,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -675,7 +690,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -698,6 +713,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA9D08E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA9D08E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -713,7 +739,7 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1561,13 +1587,13 @@
       <c r="A16" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="1" t="s">
         <v>187</v>
       </c>
     </row>
@@ -1575,13 +1601,13 @@
       <c r="A17" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="1" t="s">
         <v>190</v>
       </c>
     </row>
@@ -1603,9 +1629,15 @@
       <c r="A19" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">

--- a/- Hash Convencional.xlsx
+++ b/- Hash Convencional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053AA5A2-03AE-440D-A5F7-48914F8667EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DB2E9D-3514-47C5-926D-2F6E46793842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="231">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -481,9 +481,6 @@
     <t>Alternative (29)</t>
   </si>
   <si>
-    <t>Alternative (30)</t>
-  </si>
-  <si>
     <t>2694faf0dcf3ab267e58d7ace2f8c7fd</t>
   </si>
   <si>
@@ -635,6 +632,105 @@
   </si>
   <si>
     <t>662b29a7ae7fe0c2e051628d020905d0faa54f05cfa1c4036801fe02219db3d7</t>
+  </si>
+  <si>
+    <t>4e9542566445e2be8dd8c831e630678eb3e989bbca56145b2053f4e15d8d7c58</t>
+  </si>
+  <si>
+    <t>33b349afcc0400c57cd6d2de01674b3a0539ff12</t>
+  </si>
+  <si>
+    <t>789663744f24ebfd5dbb96a63ea5da21</t>
+  </si>
+  <si>
+    <t>0fcecc6e44a99b0cee5578588ab66af0</t>
+  </si>
+  <si>
+    <t>de066bf5582356443284b9294d93483326dca077</t>
+  </si>
+  <si>
+    <t>d9d86bc35ef67ec738bada479d025f06efaf796241a9d07979d5de636bb04026</t>
+  </si>
+  <si>
+    <t>dc4403b4469c13c1b10ea8d4bc7fd0a7</t>
+  </si>
+  <si>
+    <t>283a4149067cd7112c8aca7f57a0cf7d836e425e</t>
+  </si>
+  <si>
+    <t>7f138de590eb7430142594ac0e78d31106ad42e05813de831424f3c0d3d3caf2</t>
+  </si>
+  <si>
+    <t>c5ac7148b36234ebce02e908164fc642a0285d9d2a4e9edc5f2698d08927364c</t>
+  </si>
+  <si>
+    <t>cd396c4fc9c04aeff21460a74bf1d93174ac429c</t>
+  </si>
+  <si>
+    <t>3b130db650ac2e724e97ee4587f84094</t>
+  </si>
+  <si>
+    <t>2e2c1e2562b65a3679003ebe1b2f88c4</t>
+  </si>
+  <si>
+    <t>98c2a387c8982d1dfb612e770f709671418275b0</t>
+  </si>
+  <si>
+    <t>f8fd36fe06a060c3eb630404834652a9c9d481c9ac7afda0dcf56c71914602e5</t>
+  </si>
+  <si>
+    <t>a82fbf9979db9a774f2a39b587cd4630</t>
+  </si>
+  <si>
+    <t>9b8926d958aeab8d2629544e78880f27b5c990ed</t>
+  </si>
+  <si>
+    <t>7b1b59dc8807bba70d16e44781ccea200c0ec202510bad9b1b3da0fb2f9a660c</t>
+  </si>
+  <si>
+    <t>7404df810debaa0df786db34715bb001</t>
+  </si>
+  <si>
+    <t>58f1ac4d5e5f8334ff71275e65ee53d035d7d257</t>
+  </si>
+  <si>
+    <t>122e81b62f38f0b7e1506c17e6bad7bb767bf63d6c4b4be20f9afa86022f4c87</t>
+  </si>
+  <si>
+    <t>d83cc6552ad676ee7d3b301ac96bffe9</t>
+  </si>
+  <si>
+    <t>097ebc701af10207d9fe5350e4552f8e26c49bb1</t>
+  </si>
+  <si>
+    <t>8d4cb8aacaf7f90014313eaca144fb8e79c5d9a4369cf221ac9d25177d8bb831</t>
+  </si>
+  <si>
+    <t>8ccdaf0d49a0f0be060975b35eeadff5</t>
+  </si>
+  <si>
+    <t>4352fc2c51b45e37d7f5b26ff0b6b5c686fa7227</t>
+  </si>
+  <si>
+    <t>086b57335056cfced38e2555c9ee6816eb9667d4be8459067d30eb5d5cf773f9</t>
+  </si>
+  <si>
+    <t>7259ec2a3e23bcdc84a6ba4ecfb292e8</t>
+  </si>
+  <si>
+    <t>7fc447a1e1c49ab8c1a0e3aa64c49a2283b9d803</t>
+  </si>
+  <si>
+    <t>ff6a0993d089a173ffc913d3c0f63f888a833cf32924f289cb0e6f42ed4272c5</t>
+  </si>
+  <si>
+    <t>270fd40eace55ae9621a2f1c84105ec8</t>
+  </si>
+  <si>
+    <t>b5272e66c35daea2a3588f8ff2dc7637053e1434</t>
+  </si>
+  <si>
+    <t>872d63b489c0605d3315a61bb209d2d270a7d8cc039dbfc70ac0077057378079</t>
   </si>
 </sst>
 </file>
@@ -690,7 +786,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -713,17 +809,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA9D08E"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA9D08E"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -739,7 +824,7 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1364,12 +1449,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0BFC08-6082-4292-916D-F5AFAF8E32EA}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="67.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1420,13 +1505,13 @@
         <v>119</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1434,13 +1519,13 @@
         <v>120</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1448,13 +1533,13 @@
         <v>121</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1462,13 +1547,13 @@
         <v>122</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,13 +1561,13 @@
         <v>123</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1490,13 +1575,13 @@
         <v>124</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1504,13 +1589,13 @@
         <v>125</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,13 +1603,13 @@
         <v>126</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="7" t="s">
         <v>173</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1532,13 +1617,13 @@
         <v>127</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1546,13 +1631,13 @@
         <v>128</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1560,13 +1645,13 @@
         <v>129</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1574,55 +1659,55 @@
         <v>130</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="B16" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="C16" s="8" t="s">
         <v>187</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B17" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="C17" s="8" t="s">
         <v>190</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1630,127 +1715,182 @@
         <v>134</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>197</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D37" s="1"/>
+      <c r="B31" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>230</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/- Hash Convencional.xlsx
+++ b/- Hash Convencional.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DB2E9D-3514-47C5-926D-2F6E46793842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CD1AAD-CBD9-465D-9171-E167CA76D63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="20" r:id="rId1"/>
     <sheet name="MountainDatabase" sheetId="22" r:id="rId2"/>
-    <sheet name="WashingtonDatabase" sheetId="21" r:id="rId3"/>
+    <sheet name="PalaceDatabase" sheetId="23" r:id="rId3"/>
+    <sheet name="WashingtonDatabase" sheetId="21" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="238">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -731,6 +732,27 @@
   </si>
   <si>
     <t>872d63b489c0605d3315a61bb209d2d270a7d8cc039dbfc70ac0077057378079</t>
+  </si>
+  <si>
+    <t>Alternative (30)</t>
+  </si>
+  <si>
+    <t>675d710a331c22091307964bc074daf8</t>
+  </si>
+  <si>
+    <t>06ca0dd346e0fc6f3730b2ece7246f3a9218ce6c</t>
+  </si>
+  <si>
+    <t>4f412bb7ee4078a402fe3c3904376375f1a6311377a2ac2445a3bdaca5a60b3f</t>
+  </si>
+  <si>
+    <t>83c4f518c0c785936892b20226a57caf</t>
+  </si>
+  <si>
+    <t>cf743cdd66ac2299232375cc949c34631a4f08b9</t>
+  </si>
+  <si>
+    <t>558ee9100bcc7cbf755d46f18f0c6b6159bc3199e69b634702bc3b8b91293239</t>
   </si>
 </sst>
 </file>
@@ -1899,6 +1921,297 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD73308-E663-4598-BEC3-CCFE3639BB8F}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4653D079-C8C7-4EFD-B691-42F479BD5FAB}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
